--- a/data/industry/CFM/SODIMM.xlsx
+++ b/data/industry/CFM/SODIMM.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="20417"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\PycharmProjects\AlternativeData\data\industry\CFM\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krm\PycharmProjects\AlternativeData\data\industry\CFM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FD7B3FA4-072C-4D10-BBEB-42AD7549E79E}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B5CD5A0C-6ECA-40D7-A97D-8FFAEC4C86D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DDR4 SODIMM 4GB 3200" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="123" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="9">
   <si>
     <t>Base Date</t>
     <phoneticPr fontId="3" type="noConversion"/>
@@ -133,7 +133,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="177" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -164,6 +164,13 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="179" fontId="4" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="176" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="쉼표 [0]" xfId="1" builtinId="6"/>
@@ -445,15 +452,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G35"/>
-  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:G39"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="12.75" style="8" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.25" style="8" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.375" style="6" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.625" style="7" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.69921875" style="8" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.19921875" style="8" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.3984375" style="6" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.59765625" style="7" bestFit="1" customWidth="1"/>
     <col min="5" max="6" width="9" style="11"/>
-    <col min="7" max="7" width="11.25" style="11" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.19921875" style="11" bestFit="1" customWidth="1"/>
     <col min="8" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
@@ -1259,6 +1266,98 @@
         <v>45.4</v>
       </c>
       <c r="G35" s="11">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A36" s="8">
+        <v>46112</v>
+      </c>
+      <c r="B36" s="8">
+        <v>46112</v>
+      </c>
+      <c r="C36" s="6">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D36" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E36" s="11">
+        <v>39.5</v>
+      </c>
+      <c r="F36" s="11">
+        <v>45.4</v>
+      </c>
+      <c r="G36" s="11">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A37" s="8">
+        <v>46119</v>
+      </c>
+      <c r="B37" s="8">
+        <v>46119</v>
+      </c>
+      <c r="C37" s="6">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D37" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E37" s="11">
+        <v>39.5</v>
+      </c>
+      <c r="F37" s="11">
+        <v>45.4</v>
+      </c>
+      <c r="G37" s="11">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A38" s="8">
+        <v>46126</v>
+      </c>
+      <c r="B38" s="8">
+        <v>46126</v>
+      </c>
+      <c r="C38" s="6">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D38" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E38" s="11">
+        <v>39.5</v>
+      </c>
+      <c r="F38" s="11">
+        <v>45.4</v>
+      </c>
+      <c r="G38" s="11">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A39" s="8">
+        <v>46133</v>
+      </c>
+      <c r="B39" s="8">
+        <v>46133</v>
+      </c>
+      <c r="C39" s="6">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D39" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E39" s="11">
+        <v>39.5</v>
+      </c>
+      <c r="F39" s="11">
+        <v>45.4</v>
+      </c>
+      <c r="G39" s="11">
         <v>42</v>
       </c>
     </row>
@@ -1270,15 +1369,15 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4D9F7D34-9614-456C-B66D-E33AF53643A7}">
-  <dimension ref="A1:G35"/>
-  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:G39"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="12.75" style="8" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.25" style="8" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.375" style="6" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.625" style="7" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="9" style="11"/>
-    <col min="7" max="7" width="11.25" style="11" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.69921875" style="8" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.19921875" style="8" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.3984375" style="6" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.59765625" style="7" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="9" style="14"/>
+    <col min="7" max="7" width="11.19921875" style="14" bestFit="1" customWidth="1"/>
     <col min="8" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
@@ -1295,13 +1394,13 @@
       <c r="D1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="9" t="s">
+      <c r="E1" s="12" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="9" t="s">
+      <c r="F1" s="12" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="9" t="s">
+      <c r="G1" s="12" t="s">
         <v>6</v>
       </c>
     </row>
@@ -1318,13 +1417,13 @@
       <c r="D2" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="E2" s="10">
+      <c r="E2" s="13">
         <v>20</v>
       </c>
-      <c r="F2" s="10">
+      <c r="F2" s="13">
         <v>22.5</v>
       </c>
-      <c r="G2" s="10">
+      <c r="G2" s="13">
         <v>21</v>
       </c>
     </row>
@@ -1341,13 +1440,13 @@
       <c r="D3" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="E3" s="10">
+      <c r="E3" s="13">
         <v>20</v>
       </c>
-      <c r="F3" s="10">
+      <c r="F3" s="13">
         <v>22.5</v>
       </c>
-      <c r="G3" s="10">
+      <c r="G3" s="13">
         <v>21</v>
       </c>
     </row>
@@ -1364,13 +1463,13 @@
       <c r="D4" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="E4" s="10">
+      <c r="E4" s="13">
         <v>23</v>
       </c>
-      <c r="F4" s="10">
+      <c r="F4" s="13">
         <v>28</v>
       </c>
-      <c r="G4" s="10">
+      <c r="G4" s="13">
         <v>24</v>
       </c>
     </row>
@@ -1387,13 +1486,13 @@
       <c r="D5" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="E5" s="10">
+      <c r="E5" s="13">
         <v>23</v>
       </c>
-      <c r="F5" s="10">
+      <c r="F5" s="13">
         <v>28</v>
       </c>
-      <c r="G5" s="10">
+      <c r="G5" s="13">
         <v>24</v>
       </c>
     </row>
@@ -1410,13 +1509,13 @@
       <c r="D6" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="E6" s="10">
+      <c r="E6" s="13">
         <v>23</v>
       </c>
-      <c r="F6" s="10">
+      <c r="F6" s="13">
         <v>28</v>
       </c>
-      <c r="G6" s="10">
+      <c r="G6" s="13">
         <v>24</v>
       </c>
     </row>
@@ -1433,13 +1532,13 @@
       <c r="D7" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="E7" s="10">
+      <c r="E7" s="13">
         <v>23</v>
       </c>
-      <c r="F7" s="10">
+      <c r="F7" s="13">
         <v>30</v>
       </c>
-      <c r="G7" s="10">
+      <c r="G7" s="13">
         <v>28</v>
       </c>
     </row>
@@ -1456,13 +1555,13 @@
       <c r="D8" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="E8" s="10">
+      <c r="E8" s="13">
         <v>23</v>
       </c>
-      <c r="F8" s="10">
+      <c r="F8" s="13">
         <v>30</v>
       </c>
-      <c r="G8" s="10">
+      <c r="G8" s="13">
         <v>28</v>
       </c>
     </row>
@@ -1479,13 +1578,13 @@
       <c r="D9" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="E9" s="10">
+      <c r="E9" s="13">
         <v>23</v>
       </c>
-      <c r="F9" s="10">
+      <c r="F9" s="13">
         <v>30</v>
       </c>
-      <c r="G9" s="10">
+      <c r="G9" s="13">
         <v>28</v>
       </c>
     </row>
@@ -1502,13 +1601,13 @@
       <c r="D10" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="E10" s="10">
+      <c r="E10" s="13">
         <v>23</v>
       </c>
-      <c r="F10" s="10">
+      <c r="F10" s="13">
         <v>30</v>
       </c>
-      <c r="G10" s="10">
+      <c r="G10" s="13">
         <v>28</v>
       </c>
     </row>
@@ -1525,13 +1624,13 @@
       <c r="D11" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="E11" s="10">
+      <c r="E11" s="13">
         <v>23</v>
       </c>
-      <c r="F11" s="10">
+      <c r="F11" s="13">
         <v>30</v>
       </c>
-      <c r="G11" s="10">
+      <c r="G11" s="13">
         <v>28</v>
       </c>
     </row>
@@ -1548,13 +1647,13 @@
       <c r="D12" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="E12" s="10">
+      <c r="E12" s="13">
         <v>23</v>
       </c>
-      <c r="F12" s="10">
+      <c r="F12" s="13">
         <v>30</v>
       </c>
-      <c r="G12" s="10">
+      <c r="G12" s="13">
         <v>28</v>
       </c>
     </row>
@@ -1571,13 +1670,13 @@
       <c r="D13" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="E13" s="10">
+      <c r="E13" s="13">
         <v>28</v>
       </c>
-      <c r="F13" s="10">
+      <c r="F13" s="13">
         <v>35</v>
       </c>
-      <c r="G13" s="10">
+      <c r="G13" s="13">
         <v>33</v>
       </c>
     </row>
@@ -1594,13 +1693,13 @@
       <c r="D14" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="E14" s="10">
+      <c r="E14" s="13">
         <v>28</v>
       </c>
-      <c r="F14" s="10">
+      <c r="F14" s="13">
         <v>35</v>
       </c>
-      <c r="G14" s="10">
+      <c r="G14" s="13">
         <v>33</v>
       </c>
     </row>
@@ -1617,13 +1716,13 @@
       <c r="D15" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="E15" s="10">
+      <c r="E15" s="13">
         <v>31</v>
       </c>
-      <c r="F15" s="10">
+      <c r="F15" s="13">
         <v>38</v>
       </c>
-      <c r="G15" s="10">
+      <c r="G15" s="13">
         <v>36</v>
       </c>
     </row>
@@ -1640,13 +1739,13 @@
       <c r="D16" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="E16" s="10">
+      <c r="E16" s="13">
         <v>34</v>
       </c>
-      <c r="F16" s="10">
+      <c r="F16" s="13">
         <v>41</v>
       </c>
-      <c r="G16" s="10">
+      <c r="G16" s="13">
         <v>39</v>
       </c>
     </row>
@@ -1663,13 +1762,13 @@
       <c r="D17" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="E17" s="10">
+      <c r="E17" s="13">
         <v>40</v>
       </c>
-      <c r="F17" s="10">
+      <c r="F17" s="13">
         <v>47</v>
       </c>
-      <c r="G17" s="10">
+      <c r="G17" s="13">
         <v>45</v>
       </c>
     </row>
@@ -1686,13 +1785,13 @@
       <c r="D18" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="E18" s="10">
+      <c r="E18" s="13">
         <v>50</v>
       </c>
-      <c r="F18" s="10">
+      <c r="F18" s="13">
         <v>57</v>
       </c>
-      <c r="G18" s="10">
+      <c r="G18" s="13">
         <v>55</v>
       </c>
     </row>
@@ -1709,13 +1808,13 @@
       <c r="D19" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="E19" s="10">
+      <c r="E19" s="13">
         <v>50</v>
       </c>
-      <c r="F19" s="10">
+      <c r="F19" s="13">
         <v>57</v>
       </c>
-      <c r="G19" s="10">
+      <c r="G19" s="13">
         <v>55</v>
       </c>
     </row>
@@ -1732,13 +1831,13 @@
       <c r="D20" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="E20" s="10">
+      <c r="E20" s="13">
         <v>55</v>
       </c>
-      <c r="F20" s="10">
+      <c r="F20" s="13">
         <v>62</v>
       </c>
-      <c r="G20" s="10">
+      <c r="G20" s="13">
         <v>60</v>
       </c>
     </row>
@@ -1755,13 +1854,13 @@
       <c r="D21" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="E21" s="10">
+      <c r="E21" s="13">
         <v>55</v>
       </c>
-      <c r="F21" s="10">
+      <c r="F21" s="13">
         <v>62</v>
       </c>
-      <c r="G21" s="10">
+      <c r="G21" s="13">
         <v>60</v>
       </c>
     </row>
@@ -1778,13 +1877,13 @@
       <c r="D22" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="E22" s="10">
+      <c r="E22" s="13">
         <v>57</v>
       </c>
-      <c r="F22" s="10">
+      <c r="F22" s="13">
         <v>64</v>
       </c>
-      <c r="G22" s="10">
+      <c r="G22" s="13">
         <v>62</v>
       </c>
     </row>
@@ -1801,13 +1900,13 @@
       <c r="D23" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="E23" s="10">
+      <c r="E23" s="13">
         <v>57</v>
       </c>
-      <c r="F23" s="10">
+      <c r="F23" s="13">
         <v>64</v>
       </c>
-      <c r="G23" s="10">
+      <c r="G23" s="13">
         <v>62</v>
       </c>
     </row>
@@ -1824,13 +1923,13 @@
       <c r="D24" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="E24" s="10">
+      <c r="E24" s="13">
         <v>57</v>
       </c>
-      <c r="F24" s="10">
+      <c r="F24" s="13">
         <v>64</v>
       </c>
-      <c r="G24" s="10">
+      <c r="G24" s="13">
         <v>62</v>
       </c>
     </row>
@@ -1847,13 +1946,13 @@
       <c r="D25" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="E25" s="10">
+      <c r="E25" s="13">
         <v>57</v>
       </c>
-      <c r="F25" s="10">
+      <c r="F25" s="13">
         <v>64</v>
       </c>
-      <c r="G25" s="10">
+      <c r="G25" s="13">
         <v>62</v>
       </c>
     </row>
@@ -1870,13 +1969,13 @@
       <c r="D26" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="E26" s="10">
+      <c r="E26" s="13">
         <v>57</v>
       </c>
-      <c r="F26" s="10">
+      <c r="F26" s="13">
         <v>64</v>
       </c>
-      <c r="G26" s="10">
+      <c r="G26" s="13">
         <v>62</v>
       </c>
     </row>
@@ -1893,13 +1992,13 @@
       <c r="D27" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="E27" s="10">
+      <c r="E27" s="13">
         <v>65</v>
       </c>
-      <c r="F27" s="10">
+      <c r="F27" s="13">
         <v>72</v>
       </c>
-      <c r="G27" s="10">
+      <c r="G27" s="13">
         <v>70</v>
       </c>
     </row>
@@ -1916,13 +2015,13 @@
       <c r="D28" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="E28" s="11">
+      <c r="E28" s="14">
         <v>65</v>
       </c>
-      <c r="F28" s="11">
+      <c r="F28" s="14">
         <v>72</v>
       </c>
-      <c r="G28" s="11">
+      <c r="G28" s="14">
         <v>70</v>
       </c>
     </row>
@@ -1939,13 +2038,13 @@
       <c r="D29" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="E29" s="11">
+      <c r="E29" s="14">
         <v>75</v>
       </c>
-      <c r="F29" s="11">
+      <c r="F29" s="14">
         <v>82</v>
       </c>
-      <c r="G29" s="11">
+      <c r="G29" s="14">
         <v>80</v>
       </c>
     </row>
@@ -1962,13 +2061,13 @@
       <c r="D30" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="E30" s="11">
+      <c r="E30" s="14">
         <v>75</v>
       </c>
-      <c r="F30" s="11">
+      <c r="F30" s="14">
         <v>82</v>
       </c>
-      <c r="G30" s="11">
+      <c r="G30" s="14">
         <v>80</v>
       </c>
     </row>
@@ -1985,13 +2084,13 @@
       <c r="D31" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="E31" s="11">
+      <c r="E31" s="14">
         <v>75</v>
       </c>
-      <c r="F31" s="11">
+      <c r="F31" s="14">
         <v>82</v>
       </c>
-      <c r="G31" s="11">
+      <c r="G31" s="14">
         <v>80</v>
       </c>
     </row>
@@ -2008,13 +2107,13 @@
       <c r="D32" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="E32" s="11">
+      <c r="E32" s="14">
         <v>85</v>
       </c>
-      <c r="F32" s="11">
+      <c r="F32" s="14">
         <v>92</v>
       </c>
-      <c r="G32" s="11">
+      <c r="G32" s="14">
         <v>90</v>
       </c>
     </row>
@@ -2031,13 +2130,13 @@
       <c r="D33" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="E33" s="11">
+      <c r="E33" s="14">
         <v>85</v>
       </c>
-      <c r="F33" s="11">
+      <c r="F33" s="14">
         <v>92</v>
       </c>
-      <c r="G33" s="11">
+      <c r="G33" s="14">
         <v>90</v>
       </c>
     </row>
@@ -2054,13 +2153,13 @@
       <c r="D34" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="E34" s="11">
+      <c r="E34" s="14">
         <v>91</v>
       </c>
-      <c r="F34" s="11">
+      <c r="F34" s="14">
         <v>98</v>
       </c>
-      <c r="G34" s="11">
+      <c r="G34" s="14">
         <v>96</v>
       </c>
     </row>
@@ -2077,14 +2176,106 @@
       <c r="D35" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="E35" s="11">
+      <c r="E35" s="14">
         <v>91</v>
       </c>
-      <c r="F35" s="11">
+      <c r="F35" s="14">
         <v>98</v>
       </c>
-      <c r="G35" s="11">
+      <c r="G35" s="14">
         <v>96</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A36" s="8">
+        <v>46112</v>
+      </c>
+      <c r="B36" s="8">
+        <v>46112</v>
+      </c>
+      <c r="C36" s="6">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D36" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E36" s="14">
+        <v>91</v>
+      </c>
+      <c r="F36" s="14">
+        <v>98</v>
+      </c>
+      <c r="G36" s="14">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A37" s="8">
+        <v>46119</v>
+      </c>
+      <c r="B37" s="8">
+        <v>46119</v>
+      </c>
+      <c r="C37" s="6">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D37" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E37" s="14">
+        <v>91</v>
+      </c>
+      <c r="F37" s="14">
+        <v>98</v>
+      </c>
+      <c r="G37" s="14">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A38" s="8">
+        <v>46126</v>
+      </c>
+      <c r="B38" s="8">
+        <v>46126</v>
+      </c>
+      <c r="C38" s="6">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D38" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E38" s="14">
+        <v>85</v>
+      </c>
+      <c r="F38" s="14">
+        <v>92</v>
+      </c>
+      <c r="G38" s="14">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A39" s="8">
+        <v>46133</v>
+      </c>
+      <c r="B39" s="8">
+        <v>46133</v>
+      </c>
+      <c r="C39" s="6">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D39" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E39" s="14">
+        <v>85</v>
+      </c>
+      <c r="F39" s="14">
+        <v>92</v>
+      </c>
+      <c r="G39" s="14">
+        <v>90</v>
       </c>
     </row>
   </sheetData>
@@ -2095,15 +2286,15 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3EA0A4F0-C10D-4632-99CA-14E155280997}">
-  <dimension ref="A1:G35"/>
-  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:G39"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="12.75" style="8" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.25" style="8" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.375" style="6" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.625" style="7" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.69921875" style="8" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.19921875" style="8" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.3984375" style="6" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.59765625" style="7" bestFit="1" customWidth="1"/>
     <col min="5" max="6" width="9" style="11"/>
-    <col min="7" max="7" width="11.25" style="11" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.19921875" style="11" bestFit="1" customWidth="1"/>
     <col min="8" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
@@ -2912,6 +3103,98 @@
         <v>200</v>
       </c>
     </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A36" s="8">
+        <v>46112</v>
+      </c>
+      <c r="B36" s="8">
+        <v>46112</v>
+      </c>
+      <c r="C36" s="6">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D36" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E36" s="11">
+        <v>195</v>
+      </c>
+      <c r="F36" s="11">
+        <v>202</v>
+      </c>
+      <c r="G36" s="11">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A37" s="8">
+        <v>46119</v>
+      </c>
+      <c r="B37" s="8">
+        <v>46119</v>
+      </c>
+      <c r="C37" s="6">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D37" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E37" s="11">
+        <v>195</v>
+      </c>
+      <c r="F37" s="11">
+        <v>202</v>
+      </c>
+      <c r="G37" s="11">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A38" s="8">
+        <v>46126</v>
+      </c>
+      <c r="B38" s="8">
+        <v>46126</v>
+      </c>
+      <c r="C38" s="6">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D38" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E38" s="11">
+        <v>185</v>
+      </c>
+      <c r="F38" s="11">
+        <v>192</v>
+      </c>
+      <c r="G38" s="11">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A39" s="8">
+        <v>46133</v>
+      </c>
+      <c r="B39" s="8">
+        <v>46133</v>
+      </c>
+      <c r="C39" s="6">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D39" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E39" s="11">
+        <v>185</v>
+      </c>
+      <c r="F39" s="11">
+        <v>192</v>
+      </c>
+      <c r="G39" s="11">
+        <v>190</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/data/industry/CFM/SODIMM.xlsx
+++ b/data/industry/CFM/SODIMM.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krm\PycharmProjects\AlternativeData\data\industry\CFM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F1BE2C08-1AB3-4E2C-BCF8-779134C804E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{86D912DB-32B2-4FD6-A86B-D27B191ED7BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="1" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DDR4 SODIMM 4GB 3200" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="169" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="181" uniqueCount="9">
   <si>
     <t>Base Date</t>
     <phoneticPr fontId="3" type="noConversion"/>
@@ -76,9 +76,9 @@
     <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd;@"/>
     <numFmt numFmtId="165" formatCode="[$-409]h:mm:ss\ AM/PM;@"/>
     <numFmt numFmtId="166" formatCode="_(* #,##0.0_);_(* \(#,##0.0\);_(* &quot;-&quot;_);_(@_)"/>
-    <numFmt numFmtId="168" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="167" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
-  <fonts count="6">
+  <fonts count="7">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -121,6 +121,12 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -146,7 +152,7 @@
     </xf>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -184,8 +190,6 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="41" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="41" fontId="4" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -195,19 +199,19 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="168" fontId="5" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="5" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="쉼표" xfId="2" builtinId="3"/>
@@ -1452,7 +1456,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4D9F7D34-9614-456C-B66D-E33AF53643A7}">
-  <dimension ref="A1:G45"/>
+  <dimension ref="A1:G48"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6"/>
   <cols>
     <col min="1" max="1" width="12.6640625" style="8" bestFit="1" customWidth="1"/>
@@ -2374,13 +2378,13 @@
       <c r="D40" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="E40" s="15">
+      <c r="E40" s="14">
         <v>80</v>
       </c>
-      <c r="F40" s="15">
+      <c r="F40" s="14">
         <v>87</v>
       </c>
-      <c r="G40" s="15">
+      <c r="G40" s="14">
         <v>85</v>
       </c>
     </row>
@@ -2397,13 +2401,13 @@
       <c r="D41" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="E41" s="15">
+      <c r="E41" s="14">
         <v>77</v>
       </c>
-      <c r="F41" s="15">
+      <c r="F41" s="14">
         <v>84</v>
       </c>
-      <c r="G41" s="15">
+      <c r="G41" s="14">
         <v>82</v>
       </c>
     </row>
@@ -2420,13 +2424,13 @@
       <c r="D42" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="E42" s="15">
+      <c r="E42" s="14">
         <v>75</v>
       </c>
-      <c r="F42" s="15">
+      <c r="F42" s="14">
         <v>82</v>
       </c>
-      <c r="G42" s="15">
+      <c r="G42" s="14">
         <v>80</v>
       </c>
     </row>
@@ -2443,13 +2447,13 @@
       <c r="D43" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="E43" s="15">
+      <c r="E43" s="14">
         <v>65</v>
       </c>
-      <c r="F43" s="15">
+      <c r="F43" s="14">
         <v>72</v>
       </c>
-      <c r="G43" s="15">
+      <c r="G43" s="14">
         <v>70</v>
       </c>
     </row>
@@ -2466,13 +2470,13 @@
       <c r="D44" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="E44" s="15">
+      <c r="E44" s="14">
         <v>65</v>
       </c>
-      <c r="F44" s="15">
+      <c r="F44" s="14">
         <v>72</v>
       </c>
-      <c r="G44" s="15">
+      <c r="G44" s="14">
         <v>70</v>
       </c>
     </row>
@@ -2489,13 +2493,82 @@
       <c r="D45" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="E45" s="15">
+      <c r="E45" s="14">
         <v>65</v>
       </c>
-      <c r="F45" s="15">
+      <c r="F45" s="14">
         <v>72</v>
       </c>
-      <c r="G45" s="15">
+      <c r="G45" s="14">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7">
+      <c r="A46" s="8">
+        <v>46189</v>
+      </c>
+      <c r="B46" s="8">
+        <v>46189</v>
+      </c>
+      <c r="C46" s="6">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D46" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E46" s="14">
+        <v>65</v>
+      </c>
+      <c r="F46" s="14">
+        <v>72</v>
+      </c>
+      <c r="G46" s="14">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7">
+      <c r="A47" s="8">
+        <v>46196</v>
+      </c>
+      <c r="B47" s="8">
+        <v>46196</v>
+      </c>
+      <c r="C47" s="6">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D47" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E47" s="14">
+        <v>65</v>
+      </c>
+      <c r="F47" s="14">
+        <v>72</v>
+      </c>
+      <c r="G47" s="14">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7">
+      <c r="A48" s="8">
+        <v>46203</v>
+      </c>
+      <c r="B48" s="8">
+        <v>46203</v>
+      </c>
+      <c r="C48" s="6">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D48" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E48" s="14">
+        <v>65</v>
+      </c>
+      <c r="F48" s="14">
+        <v>72</v>
+      </c>
+      <c r="G48" s="14">
         <v>70</v>
       </c>
     </row>
@@ -2507,7 +2580,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3EA0A4F0-C10D-4632-99CA-14E155280997}">
-  <dimension ref="A1:G45"/>
+  <dimension ref="A1:G48"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6"/>
   <cols>
     <col min="1" max="1" width="12.6640625" style="8" bestFit="1" customWidth="1"/>
@@ -3554,6 +3627,75 @@
         <v>155</v>
       </c>
     </row>
+    <row r="46" spans="1:7">
+      <c r="A46" s="8">
+        <v>46189</v>
+      </c>
+      <c r="B46" s="8">
+        <v>46189</v>
+      </c>
+      <c r="C46" s="6">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D46" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E46" s="11">
+        <v>145</v>
+      </c>
+      <c r="F46" s="11">
+        <v>165</v>
+      </c>
+      <c r="G46" s="11">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7">
+      <c r="A47" s="8">
+        <v>46196</v>
+      </c>
+      <c r="B47" s="8">
+        <v>46196</v>
+      </c>
+      <c r="C47" s="6">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D47" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E47" s="11">
+        <v>145</v>
+      </c>
+      <c r="F47" s="11">
+        <v>165</v>
+      </c>
+      <c r="G47" s="11">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7">
+      <c r="A48" s="8">
+        <v>46203</v>
+      </c>
+      <c r="B48" s="8">
+        <v>46203</v>
+      </c>
+      <c r="C48" s="6">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D48" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E48" s="11">
+        <v>145</v>
+      </c>
+      <c r="F48" s="11">
+        <v>165</v>
+      </c>
+      <c r="G48" s="11">
+        <v>155</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3562,268 +3704,406 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5297F85F-0123-4AD4-9FF2-92367D502EFD}">
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:G8"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="12.6640625" style="21" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.21875" style="21" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.77734375" style="22" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.5546875" style="23" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="9.5546875" style="24" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="11.33203125" style="24" bestFit="1" customWidth="1"/>
-    <col min="8" max="16384" width="8.88671875" style="16"/>
+    <col min="1" max="1" width="12.6640625" style="19" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.21875" style="19" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.77734375" style="20" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.5546875" style="21" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="9.5546875" style="22" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.33203125" style="22" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
-      <c r="A1" s="17" t="s">
+      <c r="A1" s="15" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="17" t="s">
+      <c r="B1" s="15" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="18" t="s">
+      <c r="C1" s="16" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="19" t="s">
+      <c r="D1" s="17" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="20" t="s">
+      <c r="E1" s="18" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="20" t="s">
+      <c r="F1" s="18" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="20" t="s">
+      <c r="G1" s="18" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="2" spans="1:7">
-      <c r="A2" s="21">
+      <c r="A2" s="19">
         <v>46161</v>
       </c>
-      <c r="B2" s="21">
+      <c r="B2" s="19">
         <v>46161</v>
       </c>
-      <c r="C2" s="22">
-        <v>0.45833333333333298</v>
-      </c>
-      <c r="D2" s="23" t="s">
-        <v>8</v>
-      </c>
-      <c r="E2" s="24">
+      <c r="C2" s="20">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D2" s="21" t="s">
+        <v>8</v>
+      </c>
+      <c r="E2" s="22">
         <v>105</v>
       </c>
-      <c r="F2" s="24">
+      <c r="F2" s="22">
         <v>120</v>
       </c>
-      <c r="G2" s="24">
+      <c r="G2" s="22">
         <v>110</v>
       </c>
     </row>
     <row r="3" spans="1:7">
-      <c r="A3" s="21">
+      <c r="A3" s="19">
         <v>46168</v>
       </c>
-      <c r="B3" s="21">
+      <c r="B3" s="19">
         <v>46168</v>
       </c>
-      <c r="C3" s="22">
-        <v>0.45833333333333298</v>
-      </c>
-      <c r="D3" s="23" t="s">
-        <v>8</v>
-      </c>
-      <c r="E3" s="24">
+      <c r="C3" s="20">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D3" s="21" t="s">
+        <v>8</v>
+      </c>
+      <c r="E3" s="22">
         <v>105</v>
       </c>
-      <c r="F3" s="24">
+      <c r="F3" s="22">
         <v>120</v>
       </c>
-      <c r="G3" s="24">
+      <c r="G3" s="22">
         <v>110</v>
       </c>
     </row>
     <row r="4" spans="1:7">
-      <c r="A4" s="21">
+      <c r="A4" s="19">
         <v>46175</v>
       </c>
-      <c r="B4" s="21">
+      <c r="B4" s="19">
         <v>46175</v>
       </c>
-      <c r="C4" s="22">
-        <v>0.45833333333333298</v>
-      </c>
-      <c r="D4" s="23" t="s">
-        <v>8</v>
-      </c>
-      <c r="E4" s="24">
+      <c r="C4" s="20">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D4" s="21" t="s">
+        <v>8</v>
+      </c>
+      <c r="E4" s="22">
         <v>105</v>
       </c>
-      <c r="F4" s="24">
+      <c r="F4" s="22">
         <v>120</v>
       </c>
-      <c r="G4" s="24">
+      <c r="G4" s="22">
         <v>110</v>
       </c>
     </row>
     <row r="5" spans="1:7">
-      <c r="A5" s="21">
+      <c r="A5" s="19">
         <v>46182</v>
       </c>
-      <c r="B5" s="21">
+      <c r="B5" s="19">
         <v>46182</v>
       </c>
-      <c r="C5" s="22">
-        <v>0.45833333333333298</v>
-      </c>
-      <c r="D5" s="23" t="s">
-        <v>8</v>
-      </c>
-      <c r="E5" s="24">
+      <c r="C5" s="20">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D5" s="21" t="s">
+        <v>8</v>
+      </c>
+      <c r="E5" s="22">
         <v>105</v>
       </c>
-      <c r="F5" s="24">
+      <c r="F5" s="22">
         <v>120</v>
       </c>
-      <c r="G5" s="24">
+      <c r="G5" s="22">
         <v>110</v>
       </c>
     </row>
+    <row r="6" spans="1:7">
+      <c r="A6" s="19">
+        <v>46189</v>
+      </c>
+      <c r="B6" s="19">
+        <v>46189</v>
+      </c>
+      <c r="C6" s="20">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D6" s="21" t="s">
+        <v>8</v>
+      </c>
+      <c r="E6" s="22">
+        <v>105</v>
+      </c>
+      <c r="F6" s="22">
+        <v>120</v>
+      </c>
+      <c r="G6" s="22">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
+      <c r="A7" s="19">
+        <v>46196</v>
+      </c>
+      <c r="B7" s="19">
+        <v>46196</v>
+      </c>
+      <c r="C7" s="20">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D7" s="21" t="s">
+        <v>8</v>
+      </c>
+      <c r="E7" s="22">
+        <v>105</v>
+      </c>
+      <c r="F7" s="22">
+        <v>120</v>
+      </c>
+      <c r="G7" s="22">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
+      <c r="A8" s="19">
+        <v>46203</v>
+      </c>
+      <c r="B8" s="19">
+        <v>46203</v>
+      </c>
+      <c r="C8" s="20">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D8" s="21" t="s">
+        <v>8</v>
+      </c>
+      <c r="E8" s="22">
+        <v>105</v>
+      </c>
+      <c r="F8" s="22">
+        <v>120</v>
+      </c>
+      <c r="G8" s="22">
+        <v>110</v>
+      </c>
+    </row>
   </sheetData>
+  <phoneticPr fontId="6" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E39172B4-D2A0-49CA-B32F-E92273A8EC79}">
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:G8"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="12.6640625" style="21" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.21875" style="21" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.77734375" style="22" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.5546875" style="23" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="9.5546875" style="24" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="11.33203125" style="24" bestFit="1" customWidth="1"/>
-    <col min="8" max="16384" width="8.88671875" style="16"/>
+    <col min="1" max="1" width="12.6640625" style="19" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.21875" style="19" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.77734375" style="20" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.5546875" style="21" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="9.5546875" style="22" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.33203125" style="22" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
-      <c r="A1" s="17" t="s">
+      <c r="A1" s="15" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="17" t="s">
+      <c r="B1" s="15" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="18" t="s">
+      <c r="C1" s="16" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="19" t="s">
+      <c r="D1" s="17" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="20" t="s">
+      <c r="E1" s="18" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="20" t="s">
+      <c r="F1" s="18" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="20" t="s">
+      <c r="G1" s="18" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="2" spans="1:7">
-      <c r="A2" s="21">
+      <c r="A2" s="19">
         <v>46161</v>
       </c>
-      <c r="B2" s="21">
+      <c r="B2" s="19">
         <v>46161</v>
       </c>
-      <c r="C2" s="22">
-        <v>0.45833333333333298</v>
-      </c>
-      <c r="D2" s="23" t="s">
-        <v>8</v>
-      </c>
-      <c r="E2" s="24">
+      <c r="C2" s="20">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D2" s="21" t="s">
+        <v>8</v>
+      </c>
+      <c r="E2" s="22">
         <v>220</v>
       </c>
-      <c r="F2" s="24">
+      <c r="F2" s="22">
         <v>240</v>
       </c>
-      <c r="G2" s="24">
+      <c r="G2" s="22">
         <v>230</v>
       </c>
     </row>
     <row r="3" spans="1:7">
-      <c r="A3" s="21">
+      <c r="A3" s="19">
         <v>46168</v>
       </c>
-      <c r="B3" s="21">
+      <c r="B3" s="19">
         <v>46168</v>
       </c>
-      <c r="C3" s="22">
-        <v>0.45833333333333298</v>
-      </c>
-      <c r="D3" s="23" t="s">
-        <v>8</v>
-      </c>
-      <c r="E3" s="24">
+      <c r="C3" s="20">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D3" s="21" t="s">
+        <v>8</v>
+      </c>
+      <c r="E3" s="22">
         <v>220</v>
       </c>
-      <c r="F3" s="24">
+      <c r="F3" s="22">
         <v>240</v>
       </c>
-      <c r="G3" s="24">
+      <c r="G3" s="22">
         <v>230</v>
       </c>
     </row>
     <row r="4" spans="1:7">
-      <c r="A4" s="21">
+      <c r="A4" s="19">
         <v>46175</v>
       </c>
-      <c r="B4" s="21">
+      <c r="B4" s="19">
         <v>46175</v>
       </c>
-      <c r="C4" s="22">
-        <v>0.45833333333333298</v>
-      </c>
-      <c r="D4" s="23" t="s">
-        <v>8</v>
-      </c>
-      <c r="E4" s="24">
+      <c r="C4" s="20">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D4" s="21" t="s">
+        <v>8</v>
+      </c>
+      <c r="E4" s="22">
         <v>220</v>
       </c>
-      <c r="F4" s="24">
+      <c r="F4" s="22">
         <v>240</v>
       </c>
-      <c r="G4" s="24">
+      <c r="G4" s="22">
         <v>230</v>
       </c>
     </row>
     <row r="5" spans="1:7">
-      <c r="A5" s="21">
+      <c r="A5" s="19">
         <v>46182</v>
       </c>
-      <c r="B5" s="21">
+      <c r="B5" s="19">
         <v>46182</v>
       </c>
-      <c r="C5" s="22">
-        <v>0.45833333333333298</v>
-      </c>
-      <c r="D5" s="23" t="s">
-        <v>8</v>
-      </c>
-      <c r="E5" s="24">
+      <c r="C5" s="20">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D5" s="21" t="s">
+        <v>8</v>
+      </c>
+      <c r="E5" s="22">
         <v>220</v>
       </c>
-      <c r="F5" s="24">
+      <c r="F5" s="22">
         <v>240</v>
       </c>
-      <c r="G5" s="24">
+      <c r="G5" s="22">
         <v>230</v>
       </c>
     </row>
+    <row r="6" spans="1:7">
+      <c r="A6" s="19">
+        <v>46189</v>
+      </c>
+      <c r="B6" s="19">
+        <v>46189</v>
+      </c>
+      <c r="C6" s="20">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D6" s="21" t="s">
+        <v>8</v>
+      </c>
+      <c r="E6" s="22">
+        <v>225</v>
+      </c>
+      <c r="F6" s="22">
+        <v>240</v>
+      </c>
+      <c r="G6" s="22">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
+      <c r="A7" s="19">
+        <v>46196</v>
+      </c>
+      <c r="B7" s="19">
+        <v>46196</v>
+      </c>
+      <c r="C7" s="20">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D7" s="21" t="s">
+        <v>8</v>
+      </c>
+      <c r="E7" s="22">
+        <v>225</v>
+      </c>
+      <c r="F7" s="22">
+        <v>240</v>
+      </c>
+      <c r="G7" s="22">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
+      <c r="A8" s="19">
+        <v>46203</v>
+      </c>
+      <c r="B8" s="19">
+        <v>46203</v>
+      </c>
+      <c r="C8" s="20">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D8" s="21" t="s">
+        <v>8</v>
+      </c>
+      <c r="E8" s="22">
+        <v>225</v>
+      </c>
+      <c r="F8" s="22">
+        <v>240</v>
+      </c>
+      <c r="G8" s="22">
+        <v>230</v>
+      </c>
+    </row>
   </sheetData>
+  <phoneticPr fontId="6" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>